--- a/output/pdf_financials_xlsx/HLND.xlsx
+++ b/output/pdf_financials_xlsx/HLND.xlsx
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.230896</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.087862</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.230896</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.087862</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.230896</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.097862</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="49">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/HLND.xlsx
+++ b/output/pdf_financials_xlsx/HLND.xlsx
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="108">
@@ -2684,7 +2684,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
